--- a/URIARTE 630/Octubre/EXPENSAS-Octubre.xlsx
+++ b/URIARTE 630/Octubre/EXPENSAS-Octubre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\URIARTE 630\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\URIARTE 630\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD586E6-1BE9-4BA6-800D-8AAE4942A7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1D3D9F-B829-4B4F-A4EA-FD888F4E3E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -233,16 +233,16 @@
     <t>Ingreso pago de expensas en termino</t>
   </si>
   <si>
-    <t>Vto. 15/10</t>
-  </si>
-  <si>
-    <t>Liquidacion mes de SEPTIEMBRE</t>
-  </si>
-  <si>
     <t>ARTICULOS DE LIMPIEZA</t>
   </si>
   <si>
     <t>AL LLEGAR LOS TRES MESES DE ABONO DE EXPENSAS NOS ENCONTRAMOS CON LAS FACULTADES DE DESCONECTAR A LAS UNIDADES FUNCIONALES DE LA RED DE EDESUR.</t>
+  </si>
+  <si>
+    <t>Liquidacion mes de OCTUBRE</t>
+  </si>
+  <si>
+    <t>Vto. 14/11</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1031,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1184,29 +1184,9 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="13" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1222,6 +1202,12 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="13" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1231,9 +1217,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1645,10 +1647,10 @@
       <c r="C7" s="40"/>
       <c r="D7" s="40"/>
       <c r="E7" s="17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F7" s="53" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1681,7 +1683,7 @@
         <v>42</v>
       </c>
       <c r="B12" s="47"/>
-      <c r="C12" s="104">
+      <c r="C12" s="132">
         <v>71833</v>
       </c>
       <c r="D12" s="4"/>
@@ -1689,7 +1691,7 @@
         <v>28</v>
       </c>
       <c r="F12" s="31">
-        <v>-655462.99697167997</v>
+        <v>-876618.52137167996</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1697,7 +1699,7 @@
         <v>43</v>
       </c>
       <c r="B13" s="47"/>
-      <c r="C13" s="104">
+      <c r="C13" s="132">
         <v>4519.7749999999996</v>
       </c>
       <c r="D13" s="4"/>
@@ -1706,7 +1708,7 @@
       </c>
       <c r="F13" s="56">
         <f>'prorrateo '!F10</f>
-        <v>354052.05059999996</v>
+        <v>900893.91845567361</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1714,14 +1716,16 @@
         <v>56</v>
       </c>
       <c r="B14" s="47"/>
-      <c r="C14" s="45"/>
+      <c r="C14" s="133">
+        <v>95699.86</v>
+      </c>
       <c r="D14" s="24"/>
       <c r="E14" s="32" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="76">
         <f>-C37 +C31</f>
-        <v>-575207.57499999995</v>
+        <v>-678073.52500000002</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1729,7 +1733,7 @@
         <v>61</v>
       </c>
       <c r="B15" s="47"/>
-      <c r="C15" s="45">
+      <c r="C15" s="133">
         <v>140555</v>
       </c>
       <c r="D15" s="24"/>
@@ -1741,7 +1745,7 @@
         <v>37</v>
       </c>
       <c r="B16" s="55"/>
-      <c r="C16" s="104">
+      <c r="C16" s="132">
         <v>67972.039999999994</v>
       </c>
       <c r="D16" s="4"/>
@@ -1753,8 +1757,8 @@
         <v>40</v>
       </c>
       <c r="B17" s="47"/>
-      <c r="C17" s="104">
-        <v>42387.21</v>
+      <c r="C17" s="132">
+        <v>66605.47</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="32"/>
@@ -1765,8 +1769,8 @@
         <v>38</v>
       </c>
       <c r="B18" s="54"/>
-      <c r="C18" s="104">
-        <v>212390.55</v>
+      <c r="C18" s="132">
+        <v>230888.38</v>
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="33"/>
@@ -1785,7 +1789,7 @@
       <c r="B20" s="49"/>
       <c r="C20" s="106">
         <f>SUM(C12:C18)</f>
-        <v>539657.57499999995</v>
+        <v>678073.52500000002</v>
       </c>
       <c r="D20" s="10"/>
       <c r="E20" s="34" t="s">
@@ -1793,7 +1797,7 @@
       </c>
       <c r="F20" s="35">
         <f>SUM(F12:F18)</f>
-        <v>-876618.52137167996</v>
+        <v>-653798.12791600637</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -1808,36 +1812,34 @@
     </row>
     <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="47" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B22" s="47"/>
-      <c r="C22" s="45">
-        <v>35550</v>
-      </c>
+      <c r="C22" s="45"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="131" t="s">
-        <v>72</v>
-      </c>
-      <c r="F22" s="131"/>
+      <c r="E22" s="110" t="s">
+        <v>70</v>
+      </c>
+      <c r="F22" s="110"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="54"/>
       <c r="B23" s="47"/>
       <c r="C23" s="45"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="131"/>
-      <c r="F23" s="131"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="110"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="21"/>
       <c r="B24" s="22"/>
       <c r="C24" s="46">
         <f>SUM(C21:C23)</f>
-        <v>35550</v>
+        <v>0</v>
       </c>
       <c r="D24" s="4"/>
-      <c r="E24" s="131"/>
-      <c r="F24" s="131"/>
+      <c r="E24" s="110"/>
+      <c r="F24" s="110"/>
       <c r="G24" s="5"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1847,11 +1849,11 @@
       <c r="B25" s="27"/>
       <c r="C25" s="79">
         <f>+C24+C20</f>
-        <v>575207.57499999995</v>
+        <v>678073.52500000002</v>
       </c>
       <c r="D25" s="4"/>
-      <c r="E25" s="131"/>
-      <c r="F25" s="131"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
@@ -1859,22 +1861,22 @@
       </c>
       <c r="B26" s="44"/>
       <c r="C26" s="80"/>
-      <c r="E26" s="131"/>
-      <c r="F26" s="131"/>
+      <c r="E26" s="110"/>
+      <c r="F26" s="110"/>
     </row>
     <row r="27" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="131"/>
-      <c r="F27" s="131"/>
+      <c r="E27" s="110"/>
+      <c r="F27" s="110"/>
     </row>
     <row r="28" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
       <c r="B28" s="19"/>
       <c r="C28" s="81"/>
-      <c r="E28" s="131"/>
-      <c r="F28" s="131"/>
+      <c r="E28" s="110"/>
+      <c r="F28" s="110"/>
     </row>
     <row r="29" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="29"/>
@@ -1882,8 +1884,8 @@
       <c r="C29" s="82">
         <v>0</v>
       </c>
-      <c r="E29" s="131"/>
-      <c r="F29" s="131"/>
+      <c r="E29" s="110"/>
+      <c r="F29" s="110"/>
     </row>
     <row r="30" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="36"/>
@@ -1891,22 +1893,22 @@
       <c r="C30" s="82">
         <v>0</v>
       </c>
-      <c r="E30" s="131"/>
-      <c r="F30" s="131"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="110"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="42"/>
       <c r="B31" s="43"/>
       <c r="C31" s="83"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="131"/>
+      <c r="E31" s="110"/>
+      <c r="F31" s="110"/>
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="109"/>
       <c r="B32" s="109"/>
       <c r="C32" s="82"/>
-      <c r="E32" s="131"/>
-      <c r="F32" s="131"/>
+      <c r="E32" s="110"/>
+      <c r="F32" s="110"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="29"/>
@@ -1936,7 +1938,7 @@
       </c>
       <c r="C36" s="84">
         <f>C35+C25</f>
-        <v>575207.57499999995</v>
+        <v>678073.52500000002</v>
       </c>
       <c r="F36" s="5"/>
     </row>
@@ -1947,7 +1949,7 @@
       <c r="B37" s="39"/>
       <c r="C37" s="52">
         <f>+C25+C34</f>
-        <v>575207.57499999995</v>
+        <v>678073.52500000002</v>
       </c>
       <c r="E37" s="10"/>
     </row>
@@ -2029,7 +2031,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T116"/>
+  <dimension ref="A1:T118"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
@@ -2049,37 +2051,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="128" t="str">
+      <c r="A1" s="120" t="str">
         <f>'detalle y gastos'!E7</f>
-        <v>Liquidacion mes de SEPTIEMBRE</v>
-      </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
+        <v>Liquidacion mes de OCTUBRE</v>
+      </c>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
       <c r="D1" s="90"/>
       <c r="E1" s="91" t="s">
         <v>35</v>
       </c>
       <c r="F1" s="90"/>
-      <c r="G1" s="123" t="s">
+      <c r="G1" s="111" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="125"/>
-      <c r="L1" s="126">
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="112"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="114">
         <f>Q1</f>
-        <v>575207.57499999995</v>
-      </c>
-      <c r="M1" s="127"/>
+        <v>678073.52500000002</v>
+      </c>
+      <c r="M1" s="115"/>
       <c r="Q1">
-        <v>575207.57499999995</v>
+        <v>678073.52500000002</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="92" t="str">
         <f>'detalle y gastos'!F7</f>
-        <v>Vto. 15/10</v>
+        <v>Vto. 14/11</v>
       </c>
       <c r="B2" s="85"/>
       <c r="C2" s="85"/>
@@ -2169,7 +2171,7 @@
       </c>
       <c r="L4" s="87" t="str">
         <f>A2</f>
-        <v>Vto. 15/10</v>
+        <v>Vto. 14/11</v>
       </c>
       <c r="M4" s="94" t="s">
         <v>65</v>
@@ -2189,23 +2191,25 @@
         <v>0.5</v>
       </c>
       <c r="E5" s="23">
-        <v>131621.04750259191</v>
-      </c>
-      <c r="F5" s="45"/>
+        <v>274010</v>
+      </c>
+      <c r="F5" s="133">
+        <v>274000</v>
+      </c>
       <c r="G5" s="88">
         <f>E5-F5</f>
-        <v>131621.04750259191</v>
+        <v>10</v>
       </c>
       <c r="H5" s="89">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
-        <v>11056.167990217722</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="I5" s="9">
         <v>0</v>
       </c>
       <c r="J5" s="23">
         <f>L$1*B5</f>
-        <v>120793.59074999999</v>
+        <v>142395.44024999999</v>
       </c>
       <c r="K5" s="9">
         <f>K$2*D5</f>
@@ -2213,11 +2217,11 @@
       </c>
       <c r="L5" s="9">
         <f>J5+K5+H5+G5</f>
-        <v>263470.80624280963</v>
+        <v>142406.28024999998</v>
       </c>
       <c r="M5" s="95">
         <f>L5+L5*4%</f>
-        <v>274009.638492522</v>
+        <v>148102.53145999997</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2234,11 +2238,11 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="23">
-        <v>97669.531199999998</v>
-      </c>
-      <c r="F6" s="45">
+        <v>95715</v>
+      </c>
+      <c r="F6" s="133">
         <f>E6</f>
-        <v>97669.531199999998</v>
+        <v>95715</v>
       </c>
       <c r="G6" s="88">
         <f t="shared" ref="G6:G9" si="0">E6-F6</f>
@@ -2253,7 +2257,7 @@
       </c>
       <c r="J6" s="23">
         <f>L$1*B6</f>
-        <v>92033.212</v>
+        <v>108491.76400000001</v>
       </c>
       <c r="K6" s="9">
         <f>K$2*D6</f>
@@ -2261,11 +2265,11 @@
       </c>
       <c r="L6" s="9">
         <f t="shared" ref="L6:L9" si="2">J6+K6+H6+G6</f>
-        <v>92033.212</v>
+        <v>108491.76400000001</v>
       </c>
       <c r="M6" s="95">
         <f t="shared" ref="M6:M9" si="3">L6+L6*4%</f>
-        <v>95714.540479999996</v>
+        <v>112831.43456000001</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2280,32 +2284,35 @@
       </c>
       <c r="D7" s="51"/>
       <c r="E7" s="23">
-        <v>267151.04885209748</v>
-      </c>
-      <c r="F7" s="45"/>
+        <v>410385.32770567364</v>
+      </c>
+      <c r="F7" s="133">
+        <f>E7</f>
+        <v>410385.32770567364</v>
+      </c>
       <c r="G7" s="88">
         <f t="shared" si="0"/>
-        <v>267151.04885209748</v>
+        <v>0</v>
       </c>
       <c r="H7" s="89">
         <f t="shared" si="1"/>
-        <v>22440.688103576191</v>
+        <v>0</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="23">
         <f>L$1*B7</f>
-        <v>120793.59074999999</v>
+        <v>142395.44024999999</v>
       </c>
       <c r="K7" s="9">
         <v>0</v>
       </c>
       <c r="L7" s="9">
         <f t="shared" si="2"/>
-        <v>410385.32770567364</v>
+        <v>142395.44024999999</v>
       </c>
       <c r="M7" s="95">
         <f t="shared" si="3"/>
-        <v>426800.7408139006</v>
+        <v>148091.25785999998</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2320,11 +2327,11 @@
       </c>
       <c r="D8" s="51"/>
       <c r="E8" s="23">
-        <v>128191.25969999998</v>
-      </c>
-      <c r="F8" s="45">
+        <v>120793.59074999999</v>
+      </c>
+      <c r="F8" s="133">
         <f>E8</f>
-        <v>128191.25969999998</v>
+        <v>120793.59074999999</v>
       </c>
       <c r="G8" s="88">
         <f t="shared" si="0"/>
@@ -2337,18 +2344,18 @@
       <c r="I8" s="9"/>
       <c r="J8" s="23">
         <f>L$1*B8</f>
-        <v>120793.59074999999</v>
+        <v>142395.44024999999</v>
       </c>
       <c r="K8" s="9">
         <v>0</v>
       </c>
       <c r="L8" s="9">
         <f t="shared" si="2"/>
-        <v>120793.59074999999</v>
+        <v>142395.44024999999</v>
       </c>
       <c r="M8" s="95">
         <f t="shared" si="3"/>
-        <v>125625.33437999999</v>
+        <v>148091.25785999998</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2363,35 +2370,32 @@
       </c>
       <c r="D9" s="51"/>
       <c r="E9" s="23">
-        <v>128191.25969999998</v>
-      </c>
-      <c r="F9" s="45">
-        <f>E9</f>
-        <v>128191.25969999998</v>
-      </c>
+        <v>120793.59074999999</v>
+      </c>
+      <c r="F9" s="133"/>
       <c r="G9" s="88">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>120793.59074999999</v>
       </c>
       <c r="H9" s="89">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10146.661623</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="23">
         <f>L$1*B9</f>
-        <v>120793.59074999999</v>
+        <v>142395.44024999999</v>
       </c>
       <c r="K9" s="9">
         <v>0</v>
       </c>
       <c r="L9" s="9">
         <f t="shared" si="2"/>
-        <v>120793.59074999999</v>
+        <v>273335.69262299995</v>
       </c>
       <c r="M9" s="95">
         <f t="shared" si="3"/>
-        <v>125625.33437999999</v>
+        <v>284269.12032791995</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2409,19 +2413,19 @@
       </c>
       <c r="E10" s="100">
         <f>SUM(E5:E9)</f>
-        <v>752824.14695468929</v>
+        <v>1021697.5092056736</v>
       </c>
       <c r="F10" s="100">
         <f>SUM(F5:F9)</f>
-        <v>354052.05059999996</v>
+        <v>900893.91845567361</v>
       </c>
       <c r="G10" s="100">
         <f t="shared" si="4"/>
-        <v>131621.04750259191</v>
+        <v>10</v>
       </c>
       <c r="H10" s="100">
         <f t="shared" si="4"/>
-        <v>11056.167990217722</v>
+        <v>0.84000000000000008</v>
       </c>
       <c r="I10" s="101">
         <f t="shared" si="4"/>
@@ -2429,7 +2433,7 @@
       </c>
       <c r="J10" s="102">
         <f>SUM(J5:J9)</f>
-        <v>575207.57499999995</v>
+        <v>678073.52499999991</v>
       </c>
       <c r="K10" s="102">
         <f t="shared" si="4"/>
@@ -2437,56 +2441,56 @@
       </c>
       <c r="L10" s="100">
         <f>SUM(L5:L9)</f>
-        <v>1007476.5274484833</v>
+        <v>809024.6173729999</v>
       </c>
       <c r="M10" s="103">
         <f>SUM(M5:M9)</f>
-        <v>1047775.5885464227</v>
+        <v>841385.60206791991</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="130"/>
-      <c r="B11" s="130"/>
-      <c r="C11" s="130"/>
-      <c r="D11" s="130"/>
-      <c r="E11" s="130"/>
-      <c r="F11" s="130"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="130"/>
-      <c r="I11" s="130"/>
-      <c r="J11" s="130"/>
-      <c r="K11" s="130"/>
-      <c r="L11" s="130"/>
-      <c r="M11" s="130"/>
+      <c r="A11" s="122"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
+      <c r="F11" s="122"/>
+      <c r="G11" s="122"/>
+      <c r="H11" s="122"/>
+      <c r="I11" s="122"/>
+      <c r="J11" s="122"/>
+      <c r="K11" s="122"/>
+      <c r="L11" s="122"/>
+      <c r="M11" s="122"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="117" t="s">
+    <row r="13" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="118"/>
-      <c r="G14" s="118"/>
-      <c r="H14" s="118"/>
-      <c r="I14" s="115"/>
+      <c r="D14" s="124"/>
+      <c r="E14" s="124"/>
+      <c r="F14" s="124"/>
+      <c r="G14" s="124"/>
+      <c r="H14" s="124"/>
+      <c r="I14" s="119"/>
       <c r="J14" s="58"/>
       <c r="K14" s="59"/>
       <c r="L14" s="63"/>
     </row>
-    <row r="15" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="119" t="s">
+    <row r="15" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="118"/>
-      <c r="G15" s="118"/>
-      <c r="H15" s="118"/>
-      <c r="I15" s="115"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="124"/>
+      <c r="I15" s="119"/>
       <c r="J15" s="60"/>
       <c r="K15" s="61"/>
       <c r="L15" s="63"/>
@@ -2497,7 +2501,7 @@
         <v>96550</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C16" s="58"/>
       <c r="D16" s="62"/>
       <c r="E16" s="62"/>
@@ -2517,7 +2521,7 @@
         <v>27991.75</v>
       </c>
     </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C17" s="60" t="s">
         <v>48</v>
       </c>
@@ -2539,7 +2543,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C18" s="64"/>
       <c r="D18" s="65"/>
       <c r="E18" s="65"/>
@@ -2557,21 +2561,21 @@
         <v>24923.78</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.25">
-      <c r="C19" s="120" t="s">
+    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="121"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
-      <c r="G19" s="121"/>
-      <c r="H19" s="121"/>
-      <c r="I19" s="122"/>
+      <c r="D19" s="127"/>
+      <c r="E19" s="127"/>
+      <c r="F19" s="127"/>
+      <c r="G19" s="127"/>
+      <c r="H19" s="127"/>
+      <c r="I19" s="128"/>
       <c r="J19" s="60"/>
       <c r="K19" s="61"/>
       <c r="L19" s="63"/>
     </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C20" s="60"/>
       <c r="D20" s="63"/>
       <c r="E20" s="63"/>
@@ -2589,7 +2593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C21" s="60" t="s">
         <v>50</v>
       </c>
@@ -2604,13 +2608,13 @@
       </c>
       <c r="H21" s="67"/>
       <c r="I21" s="61"/>
-      <c r="J21" s="116" t="s">
+      <c r="J21" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="K21" s="111"/>
+      <c r="K21" s="130"/>
       <c r="L21" s="77"/>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C22" s="60" t="s">
         <v>53</v>
       </c>
@@ -2629,7 +2633,7 @@
       <c r="K22" s="61"/>
       <c r="L22" s="63"/>
     </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C23" s="60"/>
       <c r="D23" s="63"/>
       <c r="E23" s="63"/>
@@ -2637,11 +2641,11 @@
       <c r="G23" s="63"/>
       <c r="H23" s="63"/>
       <c r="I23" s="61"/>
-      <c r="J23" s="110"/>
-      <c r="K23" s="111"/>
+      <c r="J23" s="131"/>
+      <c r="K23" s="130"/>
       <c r="L23" s="77"/>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C24" s="74" t="s">
         <v>56</v>
       </c>
@@ -2651,14 +2655,14 @@
       <c r="G24" s="63"/>
       <c r="H24" s="73">
         <f>L$1/5</f>
-        <v>115041.51499999998</v>
+        <v>135614.70500000002</v>
       </c>
       <c r="I24" s="61"/>
       <c r="J24" s="60"/>
       <c r="K24" s="61"/>
       <c r="L24" s="63"/>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C25" s="75" t="s">
         <v>39</v>
       </c>
@@ -2675,7 +2679,7 @@
       <c r="K25" s="61"/>
       <c r="L25" s="63"/>
     </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C26" s="75" t="s">
         <v>37</v>
       </c>
@@ -2692,7 +2696,7 @@
       <c r="K26" s="61"/>
       <c r="L26" s="63"/>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C27" s="75" t="s">
         <v>40</v>
       </c>
@@ -2709,7 +2713,7 @@
       <c r="K27" s="61"/>
       <c r="L27" s="63"/>
     </row>
-    <row r="28" spans="3:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="75" t="s">
         <v>38</v>
       </c>
@@ -2737,7 +2741,7 @@
       <c r="K29" s="61"/>
       <c r="L29" s="63"/>
     </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C30" s="75" t="s">
         <v>44</v>
       </c>
@@ -2754,7 +2758,7 @@
       <c r="K30" s="61"/>
       <c r="L30" s="63"/>
     </row>
-    <row r="31" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C31" s="60"/>
       <c r="D31" s="63"/>
       <c r="E31" s="63"/>
@@ -2766,53 +2770,55 @@
       <c r="K31" s="70"/>
       <c r="L31" s="63"/>
     </row>
-    <row r="32" spans="3:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="112" t="s">
+    <row r="32" spans="3:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="113"/>
-      <c r="E32" s="113"/>
-      <c r="F32" s="113"/>
-      <c r="G32" s="113"/>
-      <c r="H32" s="114">
+      <c r="D32" s="117"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="117"/>
+      <c r="G32" s="117"/>
+      <c r="H32" s="118">
         <f>SUM(H24:H31)</f>
-        <v>160407.89749999999</v>
-      </c>
-      <c r="I32" s="115"/>
+        <v>180981.08750000002</v>
+      </c>
+      <c r="I32" s="119"/>
       <c r="J32" s="71"/>
       <c r="K32" s="72"/>
       <c r="L32" s="63"/>
     </row>
-    <row r="35" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="117" t="s">
+    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="36" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="118"/>
-      <c r="E36" s="118"/>
-      <c r="F36" s="118"/>
-      <c r="G36" s="118"/>
-      <c r="H36" s="118"/>
-      <c r="I36" s="115"/>
+      <c r="D36" s="124"/>
+      <c r="E36" s="124"/>
+      <c r="F36" s="124"/>
+      <c r="G36" s="124"/>
+      <c r="H36" s="124"/>
+      <c r="I36" s="119"/>
       <c r="J36" s="58"/>
       <c r="K36" s="59"/>
       <c r="L36" s="63"/>
     </row>
-    <row r="37" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="119" t="s">
+    <row r="37" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="118"/>
-      <c r="E37" s="118"/>
-      <c r="F37" s="118"/>
-      <c r="G37" s="118"/>
-      <c r="H37" s="118"/>
-      <c r="I37" s="115"/>
+      <c r="D37" s="124"/>
+      <c r="E37" s="124"/>
+      <c r="F37" s="124"/>
+      <c r="G37" s="124"/>
+      <c r="H37" s="124"/>
+      <c r="I37" s="119"/>
       <c r="J37" s="60"/>
       <c r="K37" s="61"/>
       <c r="L37" s="63"/>
     </row>
-    <row r="38" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C38" s="58"/>
       <c r="D38" s="62"/>
       <c r="E38" s="62"/>
@@ -2826,7 +2832,7 @@
       <c r="K38" s="61"/>
       <c r="L38" s="63"/>
     </row>
-    <row r="39" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C39" s="60" t="s">
         <v>48</v>
       </c>
@@ -2843,7 +2849,7 @@
       <c r="K39" s="61"/>
       <c r="L39" s="63"/>
     </row>
-    <row r="40" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C40" s="64"/>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -2855,21 +2861,21 @@
       <c r="K40" s="61"/>
       <c r="L40" s="63"/>
     </row>
-    <row r="41" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C41" s="120" t="s">
+    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="121"/>
-      <c r="E41" s="121"/>
-      <c r="F41" s="121"/>
-      <c r="G41" s="121"/>
-      <c r="H41" s="121"/>
-      <c r="I41" s="122"/>
+      <c r="D41" s="127"/>
+      <c r="E41" s="127"/>
+      <c r="F41" s="127"/>
+      <c r="G41" s="127"/>
+      <c r="H41" s="127"/>
+      <c r="I41" s="128"/>
       <c r="J41" s="60"/>
       <c r="K41" s="61"/>
       <c r="L41" s="63"/>
     </row>
-    <row r="42" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C42" s="60"/>
       <c r="D42" s="63"/>
       <c r="E42" s="63"/>
@@ -2881,7 +2887,7 @@
       <c r="K42" s="61"/>
       <c r="L42" s="63"/>
     </row>
-    <row r="43" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C43" s="60" t="s">
         <v>50</v>
       </c>
@@ -2896,13 +2902,13 @@
       </c>
       <c r="H43" s="67"/>
       <c r="I43" s="61"/>
-      <c r="J43" s="116" t="s">
+      <c r="J43" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="K43" s="111"/>
+      <c r="K43" s="130"/>
       <c r="L43" s="77"/>
     </row>
-    <row r="44" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C44" s="60" t="s">
         <v>53</v>
       </c>
@@ -2921,7 +2927,7 @@
       <c r="K44" s="61"/>
       <c r="L44" s="63"/>
     </row>
-    <row r="45" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="60"/>
       <c r="D45" s="63"/>
       <c r="E45" s="63"/>
@@ -2929,11 +2935,11 @@
       <c r="G45" s="63"/>
       <c r="H45" s="63"/>
       <c r="I45" s="61"/>
-      <c r="J45" s="110"/>
-      <c r="K45" s="111"/>
+      <c r="J45" s="131"/>
+      <c r="K45" s="130"/>
       <c r="L45" s="77"/>
     </row>
-    <row r="46" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="60" t="s">
         <v>56</v>
       </c>
@@ -2943,14 +2949,14 @@
       <c r="G46" s="63"/>
       <c r="H46" s="73">
         <f>L$1/5</f>
-        <v>115041.51499999998</v>
+        <v>135614.70500000002</v>
       </c>
       <c r="I46" s="61"/>
       <c r="J46" s="60"/>
       <c r="K46" s="61"/>
       <c r="L46" s="63"/>
     </row>
-    <row r="47" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="60"/>
       <c r="D47" s="63"/>
       <c r="E47" s="63"/>
@@ -2962,7 +2968,7 @@
       <c r="K47" s="61"/>
       <c r="L47" s="63"/>
     </row>
-    <row r="48" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C48" s="60"/>
       <c r="D48" s="63"/>
       <c r="E48" s="63"/>
@@ -2974,53 +2980,54 @@
       <c r="K48" s="70"/>
       <c r="L48" s="63"/>
     </row>
-    <row r="49" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="112" t="s">
+    <row r="49" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="D49" s="113"/>
-      <c r="E49" s="113"/>
-      <c r="F49" s="113"/>
-      <c r="G49" s="113"/>
-      <c r="H49" s="114">
+      <c r="D49" s="117"/>
+      <c r="E49" s="117"/>
+      <c r="F49" s="117"/>
+      <c r="G49" s="117"/>
+      <c r="H49" s="118">
         <f>M6</f>
-        <v>95714.540479999996</v>
-      </c>
-      <c r="I49" s="115"/>
+        <v>112831.43456000001</v>
+      </c>
+      <c r="I49" s="119"/>
       <c r="J49" s="71"/>
       <c r="K49" s="72"/>
       <c r="L49" s="63"/>
     </row>
-    <row r="51" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="117" t="s">
+    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="52" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="D52" s="118"/>
-      <c r="E52" s="118"/>
-      <c r="F52" s="118"/>
-      <c r="G52" s="118"/>
-      <c r="H52" s="118"/>
-      <c r="I52" s="115"/>
+      <c r="D52" s="124"/>
+      <c r="E52" s="124"/>
+      <c r="F52" s="124"/>
+      <c r="G52" s="124"/>
+      <c r="H52" s="124"/>
+      <c r="I52" s="119"/>
       <c r="J52" s="58"/>
       <c r="K52" s="59"/>
       <c r="L52" s="63"/>
     </row>
-    <row r="53" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="119" t="s">
+    <row r="53" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D53" s="118"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="118"/>
-      <c r="G53" s="118"/>
-      <c r="H53" s="118"/>
-      <c r="I53" s="115"/>
+      <c r="D53" s="124"/>
+      <c r="E53" s="124"/>
+      <c r="F53" s="124"/>
+      <c r="G53" s="124"/>
+      <c r="H53" s="124"/>
+      <c r="I53" s="119"/>
       <c r="J53" s="60"/>
       <c r="K53" s="61"/>
       <c r="L53" s="63"/>
     </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C54" s="58"/>
       <c r="D54" s="62"/>
       <c r="E54" s="62"/>
@@ -3034,7 +3041,7 @@
       <c r="K54" s="61"/>
       <c r="L54" s="63"/>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C55" s="60" t="s">
         <v>48</v>
       </c>
@@ -3051,7 +3058,7 @@
       <c r="K55" s="61"/>
       <c r="L55" s="63"/>
     </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C56" s="64"/>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -3063,21 +3070,21 @@
       <c r="K56" s="61"/>
       <c r="L56" s="63"/>
     </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C57" s="120" t="s">
+    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="D57" s="121"/>
-      <c r="E57" s="121"/>
-      <c r="F57" s="121"/>
-      <c r="G57" s="121"/>
-      <c r="H57" s="121"/>
-      <c r="I57" s="122"/>
+      <c r="D57" s="127"/>
+      <c r="E57" s="127"/>
+      <c r="F57" s="127"/>
+      <c r="G57" s="127"/>
+      <c r="H57" s="127"/>
+      <c r="I57" s="128"/>
       <c r="J57" s="60"/>
       <c r="K57" s="61"/>
       <c r="L57" s="63"/>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C58" s="60"/>
       <c r="D58" s="63"/>
       <c r="E58" s="63"/>
@@ -3089,7 +3096,7 @@
       <c r="K58" s="61"/>
       <c r="L58" s="63"/>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C59" s="60" t="s">
         <v>50</v>
       </c>
@@ -3104,13 +3111,13 @@
       </c>
       <c r="H59" s="67"/>
       <c r="I59" s="61"/>
-      <c r="J59" s="116" t="s">
+      <c r="J59" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="K59" s="111"/>
+      <c r="K59" s="130"/>
       <c r="L59" s="77"/>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C60" s="60" t="s">
         <v>53</v>
       </c>
@@ -3129,7 +3136,7 @@
       <c r="K60" s="61"/>
       <c r="L60" s="63"/>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C61" s="60"/>
       <c r="D61" s="63"/>
       <c r="E61" s="63"/>
@@ -3137,11 +3144,11 @@
       <c r="G61" s="63"/>
       <c r="H61" s="63"/>
       <c r="I61" s="61"/>
-      <c r="J61" s="110"/>
-      <c r="K61" s="111"/>
+      <c r="J61" s="131"/>
+      <c r="K61" s="130"/>
       <c r="L61" s="77"/>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C62" s="60" t="s">
         <v>56</v>
       </c>
@@ -3151,14 +3158,14 @@
       <c r="G62" s="63"/>
       <c r="H62" s="73">
         <f>L$1/5</f>
-        <v>115041.51499999998</v>
+        <v>135614.70500000002</v>
       </c>
       <c r="I62" s="61"/>
       <c r="J62" s="60"/>
       <c r="K62" s="61"/>
       <c r="L62" s="63"/>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C63" s="75" t="s">
         <v>39</v>
       </c>
@@ -3175,7 +3182,7 @@
       <c r="K63" s="61"/>
       <c r="L63" s="63"/>
     </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C64" s="75" t="s">
         <v>37</v>
       </c>
@@ -3192,7 +3199,7 @@
       <c r="K64" s="61"/>
       <c r="L64" s="63"/>
     </row>
-    <row r="65" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C65" s="75" t="s">
         <v>40</v>
       </c>
@@ -3209,7 +3216,7 @@
       <c r="K65" s="61"/>
       <c r="L65" s="63"/>
     </row>
-    <row r="66" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C66" s="75" t="s">
         <v>38</v>
       </c>
@@ -3237,7 +3244,7 @@
       <c r="K67" s="61"/>
       <c r="L67" s="63"/>
     </row>
-    <row r="68" spans="3:12" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="75" t="s">
         <v>44</v>
       </c>
@@ -3254,7 +3261,7 @@
       <c r="K68" s="61"/>
       <c r="L68" s="63"/>
     </row>
-    <row r="69" spans="3:12" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="60"/>
       <c r="D69" s="63"/>
       <c r="E69" s="63"/>
@@ -3278,7 +3285,7 @@
       <c r="K70" s="61"/>
       <c r="L70" s="63"/>
     </row>
-    <row r="71" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C71" s="60"/>
       <c r="D71" s="63"/>
       <c r="E71" s="63"/>
@@ -3290,53 +3297,55 @@
       <c r="K71" s="70"/>
       <c r="L71" s="63"/>
     </row>
-    <row r="72" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="112" t="s">
+    <row r="72" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="D72" s="113"/>
-      <c r="E72" s="113"/>
-      <c r="F72" s="113"/>
-      <c r="G72" s="113"/>
-      <c r="H72" s="114">
+      <c r="D72" s="117"/>
+      <c r="E72" s="117"/>
+      <c r="F72" s="117"/>
+      <c r="G72" s="117"/>
+      <c r="H72" s="118">
         <f>SUM(H62:H71)</f>
-        <v>160407.89749999999</v>
-      </c>
-      <c r="I72" s="115"/>
+        <v>180981.08750000002</v>
+      </c>
+      <c r="I72" s="119"/>
       <c r="J72" s="71"/>
       <c r="K72" s="72"/>
       <c r="L72" s="63"/>
     </row>
-    <row r="75" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="117" t="s">
+    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="76" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="D76" s="118"/>
-      <c r="E76" s="118"/>
-      <c r="F76" s="118"/>
-      <c r="G76" s="118"/>
-      <c r="H76" s="118"/>
-      <c r="I76" s="115"/>
+      <c r="D76" s="124"/>
+      <c r="E76" s="124"/>
+      <c r="F76" s="124"/>
+      <c r="G76" s="124"/>
+      <c r="H76" s="124"/>
+      <c r="I76" s="119"/>
       <c r="J76" s="58"/>
       <c r="K76" s="59"/>
       <c r="L76" s="63"/>
     </row>
-    <row r="77" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="119" t="s">
+    <row r="77" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D77" s="118"/>
-      <c r="E77" s="118"/>
-      <c r="F77" s="118"/>
-      <c r="G77" s="118"/>
-      <c r="H77" s="118"/>
-      <c r="I77" s="115"/>
+      <c r="D77" s="124"/>
+      <c r="E77" s="124"/>
+      <c r="F77" s="124"/>
+      <c r="G77" s="124"/>
+      <c r="H77" s="124"/>
+      <c r="I77" s="119"/>
       <c r="J77" s="60"/>
       <c r="K77" s="61"/>
       <c r="L77" s="63"/>
     </row>
-    <row r="78" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C78" s="58"/>
       <c r="D78" s="62"/>
       <c r="E78" s="62"/>
@@ -3350,7 +3359,7 @@
       <c r="K78" s="61"/>
       <c r="L78" s="63"/>
     </row>
-    <row r="79" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C79" s="60" t="s">
         <v>48</v>
       </c>
@@ -3367,7 +3376,7 @@
       <c r="K79" s="61"/>
       <c r="L79" s="63"/>
     </row>
-    <row r="80" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C80" s="64"/>
       <c r="D80" s="65"/>
       <c r="E80" s="65"/>
@@ -3379,21 +3388,21 @@
       <c r="K80" s="61"/>
       <c r="L80" s="63"/>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C81" s="120" t="s">
+    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C81" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="D81" s="121"/>
-      <c r="E81" s="121"/>
-      <c r="F81" s="121"/>
-      <c r="G81" s="121"/>
-      <c r="H81" s="121"/>
-      <c r="I81" s="122"/>
+      <c r="D81" s="127"/>
+      <c r="E81" s="127"/>
+      <c r="F81" s="127"/>
+      <c r="G81" s="127"/>
+      <c r="H81" s="127"/>
+      <c r="I81" s="128"/>
       <c r="J81" s="60"/>
       <c r="K81" s="61"/>
       <c r="L81" s="63"/>
     </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C82" s="60"/>
       <c r="D82" s="63"/>
       <c r="E82" s="63"/>
@@ -3405,7 +3414,7 @@
       <c r="K82" s="61"/>
       <c r="L82" s="63"/>
     </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C83" s="60" t="s">
         <v>50</v>
       </c>
@@ -3420,13 +3429,13 @@
       </c>
       <c r="H83" s="67"/>
       <c r="I83" s="61"/>
-      <c r="J83" s="116" t="s">
+      <c r="J83" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="K83" s="111"/>
+      <c r="K83" s="130"/>
       <c r="L83" s="77"/>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C84" s="60" t="s">
         <v>53</v>
       </c>
@@ -3445,7 +3454,7 @@
       <c r="K84" s="61"/>
       <c r="L84" s="63"/>
     </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C85" s="60"/>
       <c r="D85" s="63"/>
       <c r="E85" s="63"/>
@@ -3453,11 +3462,11 @@
       <c r="G85" s="63"/>
       <c r="H85" s="63"/>
       <c r="I85" s="61"/>
-      <c r="J85" s="110"/>
-      <c r="K85" s="111"/>
+      <c r="J85" s="131"/>
+      <c r="K85" s="130"/>
       <c r="L85" s="77"/>
     </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C86" s="60" t="s">
         <v>56</v>
       </c>
@@ -3467,14 +3476,14 @@
       <c r="G86" s="63"/>
       <c r="H86" s="73">
         <f>L$1/5</f>
-        <v>115041.51499999998</v>
+        <v>135614.70500000002</v>
       </c>
       <c r="I86" s="61"/>
       <c r="J86" s="60"/>
       <c r="K86" s="61"/>
       <c r="L86" s="63"/>
     </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C87" s="75" t="s">
         <v>39</v>
       </c>
@@ -3491,7 +3500,7 @@
       <c r="K87" s="61"/>
       <c r="L87" s="63"/>
     </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C88" s="75" t="s">
         <v>37</v>
       </c>
@@ -3508,7 +3517,7 @@
       <c r="K88" s="61"/>
       <c r="L88" s="63"/>
     </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C89" s="75" t="s">
         <v>40</v>
       </c>
@@ -3525,7 +3534,7 @@
       <c r="K89" s="61"/>
       <c r="L89" s="63"/>
     </row>
-    <row r="90" spans="3:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="75" t="s">
         <v>38</v>
       </c>
@@ -3553,7 +3562,7 @@
       <c r="K91" s="61"/>
       <c r="L91" s="63"/>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C92" s="75" t="s">
         <v>44</v>
       </c>
@@ -3570,7 +3579,7 @@
       <c r="K92" s="70"/>
       <c r="L92" s="63"/>
     </row>
-    <row r="93" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D93" s="63"/>
       <c r="E93" s="63"/>
       <c r="F93" s="63"/>
@@ -3581,53 +3590,55 @@
       <c r="K93" s="61"/>
       <c r="L93" s="63"/>
     </row>
-    <row r="94" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C94" s="112" t="s">
+    <row r="94" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C94" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="D94" s="113"/>
-      <c r="E94" s="113"/>
-      <c r="F94" s="113"/>
-      <c r="G94" s="113"/>
-      <c r="H94" s="114">
+      <c r="D94" s="117"/>
+      <c r="E94" s="117"/>
+      <c r="F94" s="117"/>
+      <c r="G94" s="117"/>
+      <c r="H94" s="118">
         <f>SUM(H86:H93)</f>
-        <v>160407.89749999999</v>
-      </c>
-      <c r="I94" s="115"/>
+        <v>180981.08750000002</v>
+      </c>
+      <c r="I94" s="119"/>
       <c r="J94" s="71"/>
       <c r="K94" s="72"/>
       <c r="L94" s="63"/>
     </row>
-    <row r="97" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="98" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="117" t="s">
+    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="98" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C98" s="123" t="s">
         <v>46</v>
       </c>
-      <c r="D98" s="118"/>
-      <c r="E98" s="118"/>
-      <c r="F98" s="118"/>
-      <c r="G98" s="118"/>
-      <c r="H98" s="118"/>
-      <c r="I98" s="115"/>
+      <c r="D98" s="124"/>
+      <c r="E98" s="124"/>
+      <c r="F98" s="124"/>
+      <c r="G98" s="124"/>
+      <c r="H98" s="124"/>
+      <c r="I98" s="119"/>
       <c r="J98" s="58"/>
       <c r="K98" s="59"/>
       <c r="L98" s="63"/>
     </row>
-    <row r="99" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C99" s="119" t="s">
+    <row r="99" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C99" s="125" t="s">
         <v>47</v>
       </c>
-      <c r="D99" s="118"/>
-      <c r="E99" s="118"/>
-      <c r="F99" s="118"/>
-      <c r="G99" s="118"/>
-      <c r="H99" s="118"/>
-      <c r="I99" s="115"/>
+      <c r="D99" s="124"/>
+      <c r="E99" s="124"/>
+      <c r="F99" s="124"/>
+      <c r="G99" s="124"/>
+      <c r="H99" s="124"/>
+      <c r="I99" s="119"/>
       <c r="J99" s="60"/>
       <c r="K99" s="61"/>
       <c r="L99" s="63"/>
     </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C100" s="58"/>
       <c r="D100" s="62"/>
       <c r="E100" s="62"/>
@@ -3641,7 +3652,7 @@
       <c r="K100" s="61"/>
       <c r="L100" s="63"/>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C101" s="60" t="s">
         <v>48</v>
       </c>
@@ -3658,7 +3669,7 @@
       <c r="K101" s="61"/>
       <c r="L101" s="63"/>
     </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C102" s="64"/>
       <c r="D102" s="65"/>
       <c r="E102" s="65"/>
@@ -3670,21 +3681,21 @@
       <c r="K102" s="61"/>
       <c r="L102" s="63"/>
     </row>
-    <row r="103" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C103" s="120" t="s">
+    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C103" s="126" t="s">
         <v>49</v>
       </c>
-      <c r="D103" s="121"/>
-      <c r="E103" s="121"/>
-      <c r="F103" s="121"/>
-      <c r="G103" s="121"/>
-      <c r="H103" s="121"/>
-      <c r="I103" s="122"/>
+      <c r="D103" s="127"/>
+      <c r="E103" s="127"/>
+      <c r="F103" s="127"/>
+      <c r="G103" s="127"/>
+      <c r="H103" s="127"/>
+      <c r="I103" s="128"/>
       <c r="J103" s="60"/>
       <c r="K103" s="61"/>
       <c r="L103" s="63"/>
     </row>
-    <row r="104" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C104" s="60"/>
       <c r="D104" s="63"/>
       <c r="E104" s="63"/>
@@ -3696,7 +3707,7 @@
       <c r="K104" s="61"/>
       <c r="L104" s="63"/>
     </row>
-    <row r="105" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C105" s="60" t="s">
         <v>50</v>
       </c>
@@ -3711,13 +3722,13 @@
       </c>
       <c r="H105" s="67"/>
       <c r="I105" s="61"/>
-      <c r="J105" s="116" t="s">
+      <c r="J105" s="129" t="s">
         <v>52</v>
       </c>
-      <c r="K105" s="111"/>
+      <c r="K105" s="130"/>
       <c r="L105" s="77"/>
     </row>
-    <row r="106" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C106" s="60" t="s">
         <v>53</v>
       </c>
@@ -3735,7 +3746,7 @@
       <c r="K106" s="61"/>
       <c r="L106" s="63"/>
     </row>
-    <row r="107" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C107" s="60"/>
       <c r="D107" s="63"/>
       <c r="E107" s="63"/>
@@ -3743,11 +3754,11 @@
       <c r="G107" s="63"/>
       <c r="H107" s="63"/>
       <c r="I107" s="61"/>
-      <c r="J107" s="110"/>
-      <c r="K107" s="111"/>
+      <c r="J107" s="131"/>
+      <c r="K107" s="130"/>
       <c r="L107" s="77"/>
     </row>
-    <row r="108" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C108" s="60" t="s">
         <v>56</v>
       </c>
@@ -3757,14 +3768,14 @@
       <c r="G108" s="63"/>
       <c r="H108" s="73">
         <f>L$1/5</f>
-        <v>115041.51499999998</v>
+        <v>135614.70500000002</v>
       </c>
       <c r="I108" s="61"/>
       <c r="J108" s="60"/>
       <c r="K108" s="61"/>
       <c r="L108" s="63"/>
     </row>
-    <row r="109" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C109" s="75" t="s">
         <v>39</v>
       </c>
@@ -3781,7 +3792,7 @@
       <c r="K109" s="61"/>
       <c r="L109" s="63"/>
     </row>
-    <row r="110" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C110" s="75" t="s">
         <v>37</v>
       </c>
@@ -3798,7 +3809,7 @@
       <c r="K110" s="61"/>
       <c r="L110" s="63"/>
     </row>
-    <row r="111" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C111" s="75" t="s">
         <v>40</v>
       </c>
@@ -3815,7 +3826,7 @@
       <c r="K111" s="61"/>
       <c r="L111" s="63"/>
     </row>
-    <row r="112" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C112" s="75" t="s">
         <v>38</v>
       </c>
@@ -3843,7 +3854,7 @@
       <c r="K113" s="61"/>
       <c r="L113" s="63"/>
     </row>
-    <row r="114" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C114" s="75" t="s">
         <v>44</v>
       </c>
@@ -3860,7 +3871,7 @@
       <c r="K114" s="70"/>
       <c r="L114" s="63"/>
     </row>
-    <row r="115" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D115" s="63"/>
       <c r="E115" s="63"/>
       <c r="F115" s="63"/>
@@ -3871,25 +3882,50 @@
       <c r="K115" s="61"/>
       <c r="L115" s="63"/>
     </row>
-    <row r="116" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C116" s="112" t="s">
+    <row r="116" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C116" s="116" t="s">
         <v>55</v>
       </c>
-      <c r="D116" s="113"/>
-      <c r="E116" s="113"/>
-      <c r="F116" s="113"/>
-      <c r="G116" s="113"/>
-      <c r="H116" s="114">
+      <c r="D116" s="117"/>
+      <c r="E116" s="117"/>
+      <c r="F116" s="117"/>
+      <c r="G116" s="117"/>
+      <c r="H116" s="118">
         <f>SUM(H108:H115)</f>
-        <v>160407.89749999999</v>
-      </c>
-      <c r="I116" s="115"/>
+        <v>180981.08750000002</v>
+      </c>
+      <c r="I116" s="119"/>
       <c r="J116" s="71"/>
       <c r="K116" s="72"/>
       <c r="L116" s="63"/>
     </row>
+    <row r="117" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="39">
+    <mergeCell ref="J107:K107"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="C98:I98"/>
+    <mergeCell ref="C99:I99"/>
+    <mergeCell ref="C103:I103"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C77:I77"/>
+    <mergeCell ref="C81:I81"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="C52:I52"/>
+    <mergeCell ref="C53:I53"/>
+    <mergeCell ref="C57:I57"/>
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="C116:G116"/>
@@ -3906,29 +3942,6 @@
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="C37:I37"/>
     <mergeCell ref="C41:I41"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="C52:I52"/>
-    <mergeCell ref="C53:I53"/>
-    <mergeCell ref="C57:I57"/>
-    <mergeCell ref="J107:K107"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="C98:I98"/>
-    <mergeCell ref="C99:I99"/>
-    <mergeCell ref="C103:I103"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C77:I77"/>
-    <mergeCell ref="C81:I81"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H72:I72"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/URIARTE 630/Octubre/EXPENSAS-Octubre.xlsx
+++ b/URIARTE 630/Octubre/EXPENSAS-Octubre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\URIARTE 630\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1D3D9F-B829-4B4F-A4EA-FD888F4E3E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96F700CA-CFB0-4362-8DA8-148604471F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="75">
   <si>
     <t>UF</t>
   </si>
@@ -243,6 +243,12 @@
   </si>
   <si>
     <t>Vto. 14/11</t>
+  </si>
+  <si>
+    <t>TSG MES 8</t>
+  </si>
+  <si>
+    <t>TSG MES 9</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1037,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1178,6 +1184,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1187,6 +1194,29 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="13" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1202,12 +1232,6 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="50" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="13" fillId="8" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="17" fontId="1" fillId="2" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1217,25 +1241,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1603,7 +1608,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:G65"/>
+  <dimension ref="A2:G66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -1673,17 +1678,17 @@
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="108" t="s">
+      <c r="E11" s="109" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="108"/>
+      <c r="F11" s="109"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="47" t="s">
         <v>42</v>
       </c>
       <c r="B12" s="47"/>
-      <c r="C12" s="132">
+      <c r="C12" s="108">
         <v>71833</v>
       </c>
       <c r="D12" s="4"/>
@@ -1699,7 +1704,7 @@
         <v>43</v>
       </c>
       <c r="B13" s="47"/>
-      <c r="C13" s="132">
+      <c r="C13" s="108">
         <v>4519.7749999999996</v>
       </c>
       <c r="D13" s="4"/>
@@ -1713,10 +1718,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="54" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="B14" s="47"/>
-      <c r="C14" s="133">
+      <c r="C14" s="9">
         <v>95699.86</v>
       </c>
       <c r="D14" s="24"/>
@@ -1724,241 +1729,249 @@
         <v>18</v>
       </c>
       <c r="F14" s="76">
-        <f>-C37 +C31</f>
-        <v>-678073.52500000002</v>
+        <f>-C38 +C32</f>
+        <v>-774498.40500000003</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="54" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B15" s="47"/>
-      <c r="C15" s="133">
-        <v>140555</v>
+      <c r="C15" s="9">
+        <v>96424.88</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="32"/>
-      <c r="F15" s="33"/>
+      <c r="F15" s="76"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="54" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="55"/>
-      <c r="C16" s="132">
-        <v>67972.039999999994</v>
-      </c>
-      <c r="D16" s="4"/>
+        <v>61</v>
+      </c>
+      <c r="B16" s="47"/>
+      <c r="C16" s="9">
+        <v>140555</v>
+      </c>
+      <c r="D16" s="24"/>
       <c r="E16" s="32"/>
       <c r="F16" s="33"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="47"/>
-      <c r="C17" s="132">
-        <v>66605.47</v>
+        <v>37</v>
+      </c>
+      <c r="B17" s="55"/>
+      <c r="C17" s="108">
+        <v>67972.039999999994</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="32"/>
       <c r="F17" s="33"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="54" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="132">
-        <v>230888.38</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="B18" s="47"/>
+      <c r="C18" s="108">
+        <v>66605.47</v>
+      </c>
+      <c r="D18" s="4"/>
       <c r="E18" s="32"/>
       <c r="F18" s="33"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="47"/>
-      <c r="C19" s="104"/>
+        <v>38</v>
+      </c>
+      <c r="B19" s="54"/>
+      <c r="C19" s="108">
+        <v>230888.38</v>
+      </c>
       <c r="E19" s="32"/>
       <c r="F19" s="33"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="48"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="106">
-        <f>SUM(C12:C18)</f>
-        <v>678073.52500000002</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="34" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="47"/>
+      <c r="C20" s="104"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="33"/>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="48"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="106">
+        <f>SUM(C12:C19)</f>
+        <v>774498.40500000003</v>
+      </c>
+      <c r="D21" s="10"/>
+      <c r="E21" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="35">
-        <f>SUM(F12:F18)</f>
-        <v>-653798.12791600637</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="50" t="s">
+      <c r="F21" s="35">
+        <f>SUM(F12:F19)</f>
+        <v>-750223.00791600638</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="47"/>
-      <c r="C21" s="107"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="47" t="s">
+      <c r="B22" s="47"/>
+      <c r="C22" s="107"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="13"/>
+    </row>
+    <row r="23" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="47"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="110" t="s">
-        <v>70</v>
-      </c>
-      <c r="F22" s="110"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="54"/>
       <c r="B23" s="47"/>
       <c r="C23" s="45"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="110"/>
+      <c r="E23" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="111"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="21"/>
-      <c r="B24" s="22"/>
-      <c r="C24" s="46">
-        <f>SUM(C21:C23)</f>
+      <c r="A24" s="54"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="111"/>
+      <c r="F24" s="111"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="21"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="46">
+        <f>SUM(C22:C24)</f>
         <v>0</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="110"/>
-      <c r="F24" s="110"/>
-      <c r="G24" s="5"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
+      <c r="D25" s="4"/>
+      <c r="E25" s="111"/>
+      <c r="F25" s="111"/>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="79">
-        <f>+C24+C20</f>
-        <v>678073.52500000002</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
-    </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="41" t="s">
+      <c r="B26" s="27"/>
+      <c r="C26" s="79">
+        <f>+C25+C21</f>
+        <v>774498.40500000003</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="111"/>
+      <c r="F26" s="111"/>
+    </row>
+    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="44"/>
-      <c r="C26" s="80"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="110"/>
-    </row>
-    <row r="27" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+      <c r="B27" s="44"/>
+      <c r="C27" s="80"/>
+      <c r="E27" s="111"/>
+      <c r="F27" s="111"/>
+    </row>
+    <row r="28" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="E27" s="110"/>
-      <c r="F27" s="110"/>
-    </row>
-    <row r="28" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="25"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="81"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="110"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="111"/>
     </row>
     <row r="29" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="82">
-        <v>0</v>
-      </c>
-      <c r="E29" s="110"/>
-      <c r="F29" s="110"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="81"/>
+      <c r="E29" s="111"/>
+      <c r="F29" s="111"/>
     </row>
     <row r="30" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="36"/>
-      <c r="B30" s="37"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="28"/>
       <c r="C30" s="82">
         <v>0</v>
       </c>
-      <c r="E30" s="110"/>
-      <c r="F30" s="110"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="42"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="83"/>
-      <c r="E31" s="110"/>
-      <c r="F31" s="110"/>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="109"/>
-      <c r="B32" s="109"/>
-      <c r="C32" s="82"/>
-      <c r="E32" s="110"/>
-      <c r="F32" s="110"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="29"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="82">
+      <c r="E30" s="111"/>
+      <c r="F30" s="111"/>
+    </row>
+    <row r="31" spans="1:7" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="36"/>
+      <c r="B31" s="37"/>
+      <c r="C31" s="82">
         <v>0</v>
       </c>
-      <c r="F33" s="5"/>
+      <c r="E31" s="111"/>
+      <c r="F31" s="111"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="42"/>
+      <c r="B32" s="43"/>
+      <c r="C32" s="83"/>
+      <c r="E32" s="111"/>
+      <c r="F32" s="111"/>
+    </row>
+    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="110"/>
+      <c r="B33" s="110"/>
+      <c r="C33" s="82"/>
+      <c r="E33" s="111"/>
+      <c r="F33" s="111"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="38" t="s">
+      <c r="A34" s="29"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="82">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="39"/>
-      <c r="C34" s="52">
-        <f>SUM(C29:C33)</f>
+      <c r="B35" s="39"/>
+      <c r="C35" s="52">
+        <f>SUM(C30:C34)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C35" s="82"/>
-      <c r="F35" s="5"/>
-    </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+      <c r="C36" s="82"/>
+      <c r="F36" s="5"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="84">
-        <f>C35+C25</f>
-        <v>678073.52500000002</v>
-      </c>
-      <c r="F36" s="5"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="38" t="s">
+      <c r="C37" s="84">
+        <f>C36+C26</f>
+        <v>774498.40500000003</v>
+      </c>
+      <c r="F37" s="5"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="B37" s="39"/>
-      <c r="C37" s="52">
-        <f>+C25+C34</f>
-        <v>678073.52500000002</v>
-      </c>
-      <c r="E37" s="10"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D42" s="5"/>
+      <c r="B38" s="39"/>
+      <c r="C38" s="52">
+        <f>+C26+C35</f>
+        <v>774498.40500000003</v>
+      </c>
+      <c r="E38" s="10"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
+      <c r="D43" s="5"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D44" s="10"/>
@@ -1966,19 +1979,18 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="D46" s="10"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="13"/>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D47" s="10"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="11"/>
+      <c r="A59" s="12"/>
       <c r="B59" s="11"/>
-      <c r="C59" s="11"/>
+      <c r="C59" s="13"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="11"/>
@@ -2010,11 +2022,16 @@
       <c r="B65" s="11"/>
       <c r="C65" s="11"/>
     </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="11"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="E22:F32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="E23:F33"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2051,31 +2068,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="120" t="str">
+      <c r="A1" s="130" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de OCTUBRE</v>
       </c>
-      <c r="B1" s="121"/>
-      <c r="C1" s="121"/>
+      <c r="B1" s="131"/>
+      <c r="C1" s="131"/>
       <c r="D1" s="90"/>
       <c r="E1" s="91" t="s">
         <v>35</v>
       </c>
       <c r="F1" s="90"/>
-      <c r="G1" s="111" t="s">
+      <c r="G1" s="125" t="s">
         <v>32</v>
       </c>
-      <c r="H1" s="112"/>
-      <c r="I1" s="112"/>
-      <c r="J1" s="112"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="114">
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="128">
         <f>Q1</f>
-        <v>678073.52500000002</v>
-      </c>
-      <c r="M1" s="115"/>
+        <v>774498.40500000003</v>
+      </c>
+      <c r="M1" s="129"/>
       <c r="Q1">
-        <v>678073.52500000002</v>
+        <v>774498.40500000003</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -2193,7 +2210,7 @@
       <c r="E5" s="23">
         <v>274010</v>
       </c>
-      <c r="F5" s="133">
+      <c r="F5" s="9">
         <v>274000</v>
       </c>
       <c r="G5" s="88">
@@ -2209,7 +2226,7 @@
       </c>
       <c r="J5" s="23">
         <f>L$1*B5</f>
-        <v>142395.44024999999</v>
+        <v>162644.66505000001</v>
       </c>
       <c r="K5" s="9">
         <f>K$2*D5</f>
@@ -2217,11 +2234,11 @@
       </c>
       <c r="L5" s="9">
         <f>J5+K5+H5+G5</f>
-        <v>142406.28024999998</v>
+        <v>162655.50505000001</v>
       </c>
       <c r="M5" s="95">
         <f>L5+L5*4%</f>
-        <v>148102.53145999997</v>
+        <v>169161.725252</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2240,7 +2257,7 @@
       <c r="E6" s="23">
         <v>95715</v>
       </c>
-      <c r="F6" s="133">
+      <c r="F6" s="9">
         <f>E6</f>
         <v>95715</v>
       </c>
@@ -2257,7 +2274,7 @@
       </c>
       <c r="J6" s="23">
         <f>L$1*B6</f>
-        <v>108491.76400000001</v>
+        <v>123919.7448</v>
       </c>
       <c r="K6" s="9">
         <f>K$2*D6</f>
@@ -2265,11 +2282,11 @@
       </c>
       <c r="L6" s="9">
         <f t="shared" ref="L6:L9" si="2">J6+K6+H6+G6</f>
-        <v>108491.76400000001</v>
+        <v>123919.7448</v>
       </c>
       <c r="M6" s="95">
         <f t="shared" ref="M6:M9" si="3">L6+L6*4%</f>
-        <v>112831.43456000001</v>
+        <v>128876.534592</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2286,7 +2303,7 @@
       <c r="E7" s="23">
         <v>410385.32770567364</v>
       </c>
-      <c r="F7" s="133">
+      <c r="F7" s="9">
         <f>E7</f>
         <v>410385.32770567364</v>
       </c>
@@ -2301,18 +2318,18 @@
       <c r="I7" s="9"/>
       <c r="J7" s="23">
         <f>L$1*B7</f>
-        <v>142395.44024999999</v>
+        <v>162644.66505000001</v>
       </c>
       <c r="K7" s="9">
         <v>0</v>
       </c>
       <c r="L7" s="9">
         <f t="shared" si="2"/>
-        <v>142395.44024999999</v>
+        <v>162644.66505000001</v>
       </c>
       <c r="M7" s="95">
         <f t="shared" si="3"/>
-        <v>148091.25785999998</v>
+        <v>169150.45165200002</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -2329,7 +2346,7 @@
       <c r="E8" s="23">
         <v>120793.59074999999</v>
       </c>
-      <c r="F8" s="133">
+      <c r="F8" s="9">
         <f>E8</f>
         <v>120793.59074999999</v>
       </c>
@@ -2344,18 +2361,18 @@
       <c r="I8" s="9"/>
       <c r="J8" s="23">
         <f>L$1*B8</f>
-        <v>142395.44024999999</v>
+        <v>162644.66505000001</v>
       </c>
       <c r="K8" s="9">
         <v>0</v>
       </c>
       <c r="L8" s="9">
         <f t="shared" si="2"/>
-        <v>142395.44024999999</v>
+        <v>162644.66505000001</v>
       </c>
       <c r="M8" s="95">
         <f t="shared" si="3"/>
-        <v>148091.25785999998</v>
+        <v>169150.45165200002</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2372,7 +2389,7 @@
       <c r="E9" s="23">
         <v>120793.59074999999</v>
       </c>
-      <c r="F9" s="133"/>
+      <c r="F9" s="9"/>
       <c r="G9" s="88">
         <f t="shared" si="0"/>
         <v>120793.59074999999</v>
@@ -2384,18 +2401,18 @@
       <c r="I9" s="9"/>
       <c r="J9" s="23">
         <f>L$1*B9</f>
-        <v>142395.44024999999</v>
+        <v>162644.66505000001</v>
       </c>
       <c r="K9" s="9">
         <v>0</v>
       </c>
       <c r="L9" s="9">
         <f t="shared" si="2"/>
-        <v>273335.69262299995</v>
+        <v>293584.91742299998</v>
       </c>
       <c r="M9" s="95">
         <f t="shared" si="3"/>
-        <v>284269.12032791995</v>
+        <v>305328.31411991996</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2433,7 +2450,7 @@
       </c>
       <c r="J10" s="102">
         <f>SUM(J5:J9)</f>
-        <v>678073.52499999991</v>
+        <v>774498.40500000003</v>
       </c>
       <c r="K10" s="102">
         <f t="shared" si="4"/>
@@ -2441,56 +2458,56 @@
       </c>
       <c r="L10" s="100">
         <f>SUM(L5:L9)</f>
-        <v>809024.6173729999</v>
+        <v>905449.49737300002</v>
       </c>
       <c r="M10" s="103">
         <f>SUM(M5:M9)</f>
-        <v>841385.60206791991</v>
+        <v>941667.47726792004</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="122"/>
-      <c r="B11" s="122"/>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="122"/>
-      <c r="H11" s="122"/>
-      <c r="I11" s="122"/>
-      <c r="J11" s="122"/>
-      <c r="K11" s="122"/>
-      <c r="L11" s="122"/>
-      <c r="M11" s="122"/>
+      <c r="A11" s="132"/>
+      <c r="B11" s="132"/>
+      <c r="C11" s="132"/>
+      <c r="D11" s="132"/>
+      <c r="E11" s="132"/>
+      <c r="F11" s="132"/>
+      <c r="G11" s="132"/>
+      <c r="H11" s="132"/>
+      <c r="I11" s="132"/>
+      <c r="J11" s="132"/>
+      <c r="K11" s="132"/>
+      <c r="L11" s="132"/>
+      <c r="M11" s="132"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="M12" s="5"/>
     </row>
     <row r="13" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="123" t="s">
+      <c r="C14" s="119" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="124"/>
-      <c r="E14" s="124"/>
-      <c r="F14" s="124"/>
-      <c r="G14" s="124"/>
-      <c r="H14" s="124"/>
-      <c r="I14" s="119"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="120"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="120"/>
+      <c r="H14" s="120"/>
+      <c r="I14" s="117"/>
       <c r="J14" s="58"/>
       <c r="K14" s="59"/>
       <c r="L14" s="63"/>
     </row>
     <row r="15" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="125" t="s">
+      <c r="C15" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="124"/>
-      <c r="E15" s="124"/>
-      <c r="F15" s="124"/>
-      <c r="G15" s="124"/>
-      <c r="H15" s="124"/>
-      <c r="I15" s="119"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="120"/>
+      <c r="F15" s="120"/>
+      <c r="G15" s="120"/>
+      <c r="H15" s="120"/>
+      <c r="I15" s="117"/>
       <c r="J15" s="60"/>
       <c r="K15" s="61"/>
       <c r="L15" s="63"/>
@@ -2562,15 +2579,15 @@
       </c>
     </row>
     <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="126" t="s">
+      <c r="C19" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="127"/>
-      <c r="E19" s="127"/>
-      <c r="F19" s="127"/>
-      <c r="G19" s="127"/>
-      <c r="H19" s="127"/>
-      <c r="I19" s="128"/>
+      <c r="D19" s="123"/>
+      <c r="E19" s="123"/>
+      <c r="F19" s="123"/>
+      <c r="G19" s="123"/>
+      <c r="H19" s="123"/>
+      <c r="I19" s="124"/>
       <c r="J19" s="60"/>
       <c r="K19" s="61"/>
       <c r="L19" s="63"/>
@@ -2608,10 +2625,10 @@
       </c>
       <c r="H21" s="67"/>
       <c r="I21" s="61"/>
-      <c r="J21" s="129" t="s">
+      <c r="J21" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="K21" s="130"/>
+      <c r="K21" s="113"/>
       <c r="L21" s="77"/>
     </row>
     <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
@@ -2641,8 +2658,8 @@
       <c r="G23" s="63"/>
       <c r="H23" s="63"/>
       <c r="I23" s="61"/>
-      <c r="J23" s="131"/>
-      <c r="K23" s="130"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="113"/>
       <c r="L23" s="77"/>
     </row>
     <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
@@ -2655,7 +2672,7 @@
       <c r="G24" s="63"/>
       <c r="H24" s="73">
         <f>L$1/5</f>
-        <v>135614.70500000002</v>
+        <v>154899.68100000001</v>
       </c>
       <c r="I24" s="61"/>
       <c r="J24" s="60"/>
@@ -2771,18 +2788,18 @@
       <c r="L31" s="63"/>
     </row>
     <row r="32" spans="3:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="116" t="s">
+      <c r="C32" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="117"/>
-      <c r="E32" s="117"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="117"/>
-      <c r="H32" s="118">
+      <c r="D32" s="115"/>
+      <c r="E32" s="115"/>
+      <c r="F32" s="115"/>
+      <c r="G32" s="115"/>
+      <c r="H32" s="116">
         <f>SUM(H24:H31)</f>
-        <v>180981.08750000002</v>
-      </c>
-      <c r="I32" s="119"/>
+        <v>200266.06350000002</v>
+      </c>
+      <c r="I32" s="117"/>
       <c r="J32" s="71"/>
       <c r="K32" s="72"/>
       <c r="L32" s="63"/>
@@ -2791,29 +2808,29 @@
     <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="123" t="s">
+      <c r="C36" s="119" t="s">
         <v>46</v>
       </c>
-      <c r="D36" s="124"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="124"/>
-      <c r="G36" s="124"/>
-      <c r="H36" s="124"/>
-      <c r="I36" s="119"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="120"/>
+      <c r="F36" s="120"/>
+      <c r="G36" s="120"/>
+      <c r="H36" s="120"/>
+      <c r="I36" s="117"/>
       <c r="J36" s="58"/>
       <c r="K36" s="59"/>
       <c r="L36" s="63"/>
     </row>
     <row r="37" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="125" t="s">
+      <c r="C37" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="D37" s="124"/>
-      <c r="E37" s="124"/>
-      <c r="F37" s="124"/>
-      <c r="G37" s="124"/>
-      <c r="H37" s="124"/>
-      <c r="I37" s="119"/>
+      <c r="D37" s="120"/>
+      <c r="E37" s="120"/>
+      <c r="F37" s="120"/>
+      <c r="G37" s="120"/>
+      <c r="H37" s="120"/>
+      <c r="I37" s="117"/>
       <c r="J37" s="60"/>
       <c r="K37" s="61"/>
       <c r="L37" s="63"/>
@@ -2862,15 +2879,15 @@
       <c r="L40" s="63"/>
     </row>
     <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="126" t="s">
+      <c r="C41" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="D41" s="127"/>
-      <c r="E41" s="127"/>
-      <c r="F41" s="127"/>
-      <c r="G41" s="127"/>
-      <c r="H41" s="127"/>
-      <c r="I41" s="128"/>
+      <c r="D41" s="123"/>
+      <c r="E41" s="123"/>
+      <c r="F41" s="123"/>
+      <c r="G41" s="123"/>
+      <c r="H41" s="123"/>
+      <c r="I41" s="124"/>
       <c r="J41" s="60"/>
       <c r="K41" s="61"/>
       <c r="L41" s="63"/>
@@ -2902,10 +2919,10 @@
       </c>
       <c r="H43" s="67"/>
       <c r="I43" s="61"/>
-      <c r="J43" s="129" t="s">
+      <c r="J43" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="K43" s="130"/>
+      <c r="K43" s="113"/>
       <c r="L43" s="77"/>
     </row>
     <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
@@ -2935,8 +2952,8 @@
       <c r="G45" s="63"/>
       <c r="H45" s="63"/>
       <c r="I45" s="61"/>
-      <c r="J45" s="131"/>
-      <c r="K45" s="130"/>
+      <c r="J45" s="112"/>
+      <c r="K45" s="113"/>
       <c r="L45" s="77"/>
     </row>
     <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
@@ -2949,7 +2966,7 @@
       <c r="G46" s="63"/>
       <c r="H46" s="73">
         <f>L$1/5</f>
-        <v>135614.70500000002</v>
+        <v>154899.68100000001</v>
       </c>
       <c r="I46" s="61"/>
       <c r="J46" s="60"/>
@@ -2981,18 +2998,18 @@
       <c r="L48" s="63"/>
     </row>
     <row r="49" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="116" t="s">
+      <c r="C49" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="D49" s="117"/>
-      <c r="E49" s="117"/>
-      <c r="F49" s="117"/>
-      <c r="G49" s="117"/>
-      <c r="H49" s="118">
+      <c r="D49" s="115"/>
+      <c r="E49" s="115"/>
+      <c r="F49" s="115"/>
+      <c r="G49" s="115"/>
+      <c r="H49" s="116">
         <f>M6</f>
-        <v>112831.43456000001</v>
-      </c>
-      <c r="I49" s="119"/>
+        <v>128876.534592</v>
+      </c>
+      <c r="I49" s="117"/>
       <c r="J49" s="71"/>
       <c r="K49" s="72"/>
       <c r="L49" s="63"/>
@@ -3000,29 +3017,29 @@
     <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="52" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="123" t="s">
+      <c r="C52" s="119" t="s">
         <v>46</v>
       </c>
-      <c r="D52" s="124"/>
-      <c r="E52" s="124"/>
-      <c r="F52" s="124"/>
-      <c r="G52" s="124"/>
-      <c r="H52" s="124"/>
-      <c r="I52" s="119"/>
+      <c r="D52" s="120"/>
+      <c r="E52" s="120"/>
+      <c r="F52" s="120"/>
+      <c r="G52" s="120"/>
+      <c r="H52" s="120"/>
+      <c r="I52" s="117"/>
       <c r="J52" s="58"/>
       <c r="K52" s="59"/>
       <c r="L52" s="63"/>
     </row>
     <row r="53" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="125" t="s">
+      <c r="C53" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="D53" s="124"/>
-      <c r="E53" s="124"/>
-      <c r="F53" s="124"/>
-      <c r="G53" s="124"/>
-      <c r="H53" s="124"/>
-      <c r="I53" s="119"/>
+      <c r="D53" s="120"/>
+      <c r="E53" s="120"/>
+      <c r="F53" s="120"/>
+      <c r="G53" s="120"/>
+      <c r="H53" s="120"/>
+      <c r="I53" s="117"/>
       <c r="J53" s="60"/>
       <c r="K53" s="61"/>
       <c r="L53" s="63"/>
@@ -3071,15 +3088,15 @@
       <c r="L56" s="63"/>
     </row>
     <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="126" t="s">
+      <c r="C57" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="D57" s="127"/>
-      <c r="E57" s="127"/>
-      <c r="F57" s="127"/>
-      <c r="G57" s="127"/>
-      <c r="H57" s="127"/>
-      <c r="I57" s="128"/>
+      <c r="D57" s="123"/>
+      <c r="E57" s="123"/>
+      <c r="F57" s="123"/>
+      <c r="G57" s="123"/>
+      <c r="H57" s="123"/>
+      <c r="I57" s="124"/>
       <c r="J57" s="60"/>
       <c r="K57" s="61"/>
       <c r="L57" s="63"/>
@@ -3111,10 +3128,10 @@
       </c>
       <c r="H59" s="67"/>
       <c r="I59" s="61"/>
-      <c r="J59" s="129" t="s">
+      <c r="J59" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="K59" s="130"/>
+      <c r="K59" s="113"/>
       <c r="L59" s="77"/>
     </row>
     <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
@@ -3144,8 +3161,8 @@
       <c r="G61" s="63"/>
       <c r="H61" s="63"/>
       <c r="I61" s="61"/>
-      <c r="J61" s="131"/>
-      <c r="K61" s="130"/>
+      <c r="J61" s="112"/>
+      <c r="K61" s="113"/>
       <c r="L61" s="77"/>
     </row>
     <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
@@ -3158,7 +3175,7 @@
       <c r="G62" s="63"/>
       <c r="H62" s="73">
         <f>L$1/5</f>
-        <v>135614.70500000002</v>
+        <v>154899.68100000001</v>
       </c>
       <c r="I62" s="61"/>
       <c r="J62" s="60"/>
@@ -3298,18 +3315,18 @@
       <c r="L71" s="63"/>
     </row>
     <row r="72" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="116" t="s">
+      <c r="C72" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="D72" s="117"/>
-      <c r="E72" s="117"/>
-      <c r="F72" s="117"/>
-      <c r="G72" s="117"/>
-      <c r="H72" s="118">
+      <c r="D72" s="115"/>
+      <c r="E72" s="115"/>
+      <c r="F72" s="115"/>
+      <c r="G72" s="115"/>
+      <c r="H72" s="116">
         <f>SUM(H62:H71)</f>
-        <v>180981.08750000002</v>
-      </c>
-      <c r="I72" s="119"/>
+        <v>200266.06350000002</v>
+      </c>
+      <c r="I72" s="117"/>
       <c r="J72" s="71"/>
       <c r="K72" s="72"/>
       <c r="L72" s="63"/>
@@ -3318,29 +3335,29 @@
     <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="75" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="76" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="123" t="s">
+      <c r="C76" s="119" t="s">
         <v>46</v>
       </c>
-      <c r="D76" s="124"/>
-      <c r="E76" s="124"/>
-      <c r="F76" s="124"/>
-      <c r="G76" s="124"/>
-      <c r="H76" s="124"/>
-      <c r="I76" s="119"/>
+      <c r="D76" s="120"/>
+      <c r="E76" s="120"/>
+      <c r="F76" s="120"/>
+      <c r="G76" s="120"/>
+      <c r="H76" s="120"/>
+      <c r="I76" s="117"/>
       <c r="J76" s="58"/>
       <c r="K76" s="59"/>
       <c r="L76" s="63"/>
     </row>
     <row r="77" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="125" t="s">
+      <c r="C77" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="D77" s="124"/>
-      <c r="E77" s="124"/>
-      <c r="F77" s="124"/>
-      <c r="G77" s="124"/>
-      <c r="H77" s="124"/>
-      <c r="I77" s="119"/>
+      <c r="D77" s="120"/>
+      <c r="E77" s="120"/>
+      <c r="F77" s="120"/>
+      <c r="G77" s="120"/>
+      <c r="H77" s="120"/>
+      <c r="I77" s="117"/>
       <c r="J77" s="60"/>
       <c r="K77" s="61"/>
       <c r="L77" s="63"/>
@@ -3389,15 +3406,15 @@
       <c r="L80" s="63"/>
     </row>
     <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C81" s="126" t="s">
+      <c r="C81" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="D81" s="127"/>
-      <c r="E81" s="127"/>
-      <c r="F81" s="127"/>
-      <c r="G81" s="127"/>
-      <c r="H81" s="127"/>
-      <c r="I81" s="128"/>
+      <c r="D81" s="123"/>
+      <c r="E81" s="123"/>
+      <c r="F81" s="123"/>
+      <c r="G81" s="123"/>
+      <c r="H81" s="123"/>
+      <c r="I81" s="124"/>
       <c r="J81" s="60"/>
       <c r="K81" s="61"/>
       <c r="L81" s="63"/>
@@ -3429,10 +3446,10 @@
       </c>
       <c r="H83" s="67"/>
       <c r="I83" s="61"/>
-      <c r="J83" s="129" t="s">
+      <c r="J83" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="K83" s="130"/>
+      <c r="K83" s="113"/>
       <c r="L83" s="77"/>
     </row>
     <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
@@ -3462,8 +3479,8 @@
       <c r="G85" s="63"/>
       <c r="H85" s="63"/>
       <c r="I85" s="61"/>
-      <c r="J85" s="131"/>
-      <c r="K85" s="130"/>
+      <c r="J85" s="112"/>
+      <c r="K85" s="113"/>
       <c r="L85" s="77"/>
     </row>
     <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
@@ -3476,7 +3493,7 @@
       <c r="G86" s="63"/>
       <c r="H86" s="73">
         <f>L$1/5</f>
-        <v>135614.70500000002</v>
+        <v>154899.68100000001</v>
       </c>
       <c r="I86" s="61"/>
       <c r="J86" s="60"/>
@@ -3591,18 +3608,18 @@
       <c r="L93" s="63"/>
     </row>
     <row r="94" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C94" s="116" t="s">
+      <c r="C94" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="D94" s="117"/>
-      <c r="E94" s="117"/>
-      <c r="F94" s="117"/>
-      <c r="G94" s="117"/>
-      <c r="H94" s="118">
+      <c r="D94" s="115"/>
+      <c r="E94" s="115"/>
+      <c r="F94" s="115"/>
+      <c r="G94" s="115"/>
+      <c r="H94" s="116">
         <f>SUM(H86:H93)</f>
-        <v>180981.08750000002</v>
-      </c>
-      <c r="I94" s="119"/>
+        <v>200266.06350000002</v>
+      </c>
+      <c r="I94" s="117"/>
       <c r="J94" s="71"/>
       <c r="K94" s="72"/>
       <c r="L94" s="63"/>
@@ -3611,29 +3628,29 @@
     <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="97" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="98" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="123" t="s">
+      <c r="C98" s="119" t="s">
         <v>46</v>
       </c>
-      <c r="D98" s="124"/>
-      <c r="E98" s="124"/>
-      <c r="F98" s="124"/>
-      <c r="G98" s="124"/>
-      <c r="H98" s="124"/>
-      <c r="I98" s="119"/>
+      <c r="D98" s="120"/>
+      <c r="E98" s="120"/>
+      <c r="F98" s="120"/>
+      <c r="G98" s="120"/>
+      <c r="H98" s="120"/>
+      <c r="I98" s="117"/>
       <c r="J98" s="58"/>
       <c r="K98" s="59"/>
       <c r="L98" s="63"/>
     </row>
     <row r="99" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C99" s="125" t="s">
+      <c r="C99" s="121" t="s">
         <v>47</v>
       </c>
-      <c r="D99" s="124"/>
-      <c r="E99" s="124"/>
-      <c r="F99" s="124"/>
-      <c r="G99" s="124"/>
-      <c r="H99" s="124"/>
-      <c r="I99" s="119"/>
+      <c r="D99" s="120"/>
+      <c r="E99" s="120"/>
+      <c r="F99" s="120"/>
+      <c r="G99" s="120"/>
+      <c r="H99" s="120"/>
+      <c r="I99" s="117"/>
       <c r="J99" s="60"/>
       <c r="K99" s="61"/>
       <c r="L99" s="63"/>
@@ -3682,15 +3699,15 @@
       <c r="L102" s="63"/>
     </row>
     <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C103" s="126" t="s">
+      <c r="C103" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="D103" s="127"/>
-      <c r="E103" s="127"/>
-      <c r="F103" s="127"/>
-      <c r="G103" s="127"/>
-      <c r="H103" s="127"/>
-      <c r="I103" s="128"/>
+      <c r="D103" s="123"/>
+      <c r="E103" s="123"/>
+      <c r="F103" s="123"/>
+      <c r="G103" s="123"/>
+      <c r="H103" s="123"/>
+      <c r="I103" s="124"/>
       <c r="J103" s="60"/>
       <c r="K103" s="61"/>
       <c r="L103" s="63"/>
@@ -3722,10 +3739,10 @@
       </c>
       <c r="H105" s="67"/>
       <c r="I105" s="61"/>
-      <c r="J105" s="129" t="s">
+      <c r="J105" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="K105" s="130"/>
+      <c r="K105" s="113"/>
       <c r="L105" s="77"/>
     </row>
     <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
@@ -3754,8 +3771,8 @@
       <c r="G107" s="63"/>
       <c r="H107" s="63"/>
       <c r="I107" s="61"/>
-      <c r="J107" s="131"/>
-      <c r="K107" s="130"/>
+      <c r="J107" s="112"/>
+      <c r="K107" s="113"/>
       <c r="L107" s="77"/>
     </row>
     <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
@@ -3768,7 +3785,7 @@
       <c r="G108" s="63"/>
       <c r="H108" s="73">
         <f>L$1/5</f>
-        <v>135614.70500000002</v>
+        <v>154899.68100000001</v>
       </c>
       <c r="I108" s="61"/>
       <c r="J108" s="60"/>
@@ -3883,18 +3900,18 @@
       <c r="L115" s="63"/>
     </row>
     <row r="116" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C116" s="116" t="s">
+      <c r="C116" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="D116" s="117"/>
-      <c r="E116" s="117"/>
-      <c r="F116" s="117"/>
-      <c r="G116" s="117"/>
-      <c r="H116" s="118">
+      <c r="D116" s="115"/>
+      <c r="E116" s="115"/>
+      <c r="F116" s="115"/>
+      <c r="G116" s="115"/>
+      <c r="H116" s="116">
         <f>SUM(H108:H115)</f>
-        <v>180981.08750000002</v>
-      </c>
-      <c r="I116" s="119"/>
+        <v>200266.06350000002</v>
+      </c>
+      <c r="I116" s="117"/>
       <c r="J116" s="71"/>
       <c r="K116" s="72"/>
       <c r="L116" s="63"/>
@@ -3903,29 +3920,6 @@
     <row r="118" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="J107:K107"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="H94:I94"/>
-    <mergeCell ref="J59:K59"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="C98:I98"/>
-    <mergeCell ref="C99:I99"/>
-    <mergeCell ref="C103:I103"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="C77:I77"/>
-    <mergeCell ref="C81:I81"/>
-    <mergeCell ref="J83:K83"/>
-    <mergeCell ref="J85:K85"/>
-    <mergeCell ref="C72:G72"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="J105:K105"/>
-    <mergeCell ref="C52:I52"/>
-    <mergeCell ref="C53:I53"/>
-    <mergeCell ref="C57:I57"/>
     <mergeCell ref="G1:K1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="C116:G116"/>
@@ -3942,6 +3936,29 @@
     <mergeCell ref="C36:I36"/>
     <mergeCell ref="C37:I37"/>
     <mergeCell ref="C41:I41"/>
+    <mergeCell ref="J43:K43"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="J105:K105"/>
+    <mergeCell ref="C52:I52"/>
+    <mergeCell ref="C53:I53"/>
+    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="J107:K107"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="H94:I94"/>
+    <mergeCell ref="J59:K59"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="C98:I98"/>
+    <mergeCell ref="C99:I99"/>
+    <mergeCell ref="C103:I103"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="C77:I77"/>
+    <mergeCell ref="C81:I81"/>
+    <mergeCell ref="J83:K83"/>
+    <mergeCell ref="J85:K85"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="H72:I72"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
